--- a/output/value_pick.xlsx
+++ b/output/value_pick.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,100 +429,115 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>cash_from_operations_cr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>net_profit_margin_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>roce_percentage</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>market_cap_crore</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>pe_ratio</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>pb_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>dividend_yield_pct</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>net_profit</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>opm_percentage</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>broad_sector</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>dividend_payout_ratio_pct</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
         <is>
           <t>composite_quality_score</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>roce_percentage</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>market_cap_crore</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>pe_ratio</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>pb_ratio</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>dividend_yield_pct</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>net_profit</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>opm_percentage</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>broad_sector</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>dividend_payout_ratio_pct</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>sector_relative_score</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
         <is>
           <t>revenue_cagr_3yr</t>
         </is>
@@ -531,7 +546,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -540,72 +555,81 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11.55</v>
+        <v>7914</v>
       </c>
       <c r="D2" t="n">
-        <v>0.76</v>
+        <v>24.06</v>
       </c>
       <c r="E2" t="n">
-        <v>5.22</v>
+        <v>13.04</v>
       </c>
       <c r="F2" t="n">
-        <v>1.17</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>925</v>
+        <v>1.32</v>
       </c>
       <c r="H2" t="n">
-        <v>9.210000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="I2" t="n">
-        <v>7.56</v>
+        <v>7906</v>
       </c>
       <c r="J2" t="n">
-        <v>5.92</v>
+        <v>19.07</v>
       </c>
       <c r="K2" t="n">
-        <v>58.02</v>
+        <v>23.25</v>
       </c>
       <c r="L2" t="n">
-        <v>13.7</v>
+        <v>20.11</v>
       </c>
       <c r="M2" t="n">
-        <v>146151.16</v>
+        <v>5.73</v>
       </c>
       <c r="N2" t="n">
-        <v>9.539999999999999</v>
+        <v>2618348.58</v>
       </c>
       <c r="O2" t="n">
-        <v>2.38</v>
+        <v>9.81</v>
       </c>
       <c r="P2" t="n">
-        <v>2.18</v>
+        <v>3.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>98692</v>
+        <v>2.82</v>
       </c>
       <c r="R2" t="n">
-        <v>3020</v>
+        <v>26645</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="U2" t="n">
-        <v>20</v>
+        <v>6412</v>
+      </c>
+      <c r="T2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
       </c>
       <c r="V2" t="n">
-        <v>19.82084189180693</v>
+        <v>31</v>
+      </c>
+      <c r="W2" t="n">
+        <v>42.28401740380991</v>
+      </c>
+      <c r="X2" t="n">
+        <v>24.08396584592249</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>19.10193873049559</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -614,72 +638,81 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.54</v>
+        <v>-6274</v>
       </c>
       <c r="D3" t="n">
-        <v>1.64</v>
+        <v>15.94</v>
       </c>
       <c r="E3" t="n">
-        <v>3.76</v>
+        <v>15.76</v>
       </c>
       <c r="F3" t="n">
-        <v>0.59</v>
+        <v>12.14</v>
       </c>
       <c r="G3" t="n">
-        <v>-11245</v>
+        <v>1.9</v>
       </c>
       <c r="H3" t="n">
-        <v>5.84</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>15.32</v>
+        <v>-7559</v>
       </c>
       <c r="J3" t="n">
-        <v>16.18</v>
+        <v>17.48</v>
       </c>
       <c r="K3" t="n">
-        <v>53.41</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>26.98</v>
+        <v>55.18</v>
       </c>
       <c r="M3" t="n">
-        <v>4173085.48</v>
+        <v>6.33</v>
       </c>
       <c r="N3" t="n">
-        <v>14.22</v>
+        <v>590971.02</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8100000000000001</v>
+        <v>16.89</v>
       </c>
       <c r="P3" t="n">
-        <v>2.37</v>
+        <v>4.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>139078</v>
+        <v>2.62</v>
       </c>
       <c r="R3" t="n">
-        <v>12270</v>
+        <v>118379</v>
       </c>
       <c r="S3" t="n">
-        <v>18</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
+        <v>18869</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4102</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
         <v>21</v>
       </c>
-      <c r="V3" t="n">
-        <v>23.2535428740343</v>
+      <c r="W3" t="n">
+        <v>37.60943761161097</v>
+      </c>
+      <c r="X3" t="n">
+        <v>10.97340757490808</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>16.78883948962531</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -688,72 +721,81 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14.25</v>
+        <v>-5630</v>
       </c>
       <c r="D4" t="n">
-        <v>6.89</v>
+        <v>8.82</v>
       </c>
       <c r="E4" t="n">
-        <v>1.88</v>
+        <v>18.54</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09</v>
+        <v>1.64</v>
       </c>
       <c r="G4" t="n">
-        <v>-17468</v>
+        <v>3.76</v>
       </c>
       <c r="H4" t="n">
-        <v>15.5</v>
+        <v>0.59</v>
       </c>
       <c r="I4" t="n">
-        <v>22.08</v>
+        <v>-11245</v>
       </c>
       <c r="J4" t="n">
-        <v>15.9</v>
+        <v>5.84</v>
       </c>
       <c r="K4" t="n">
-        <v>52.45</v>
+        <v>15.32</v>
       </c>
       <c r="L4" t="n">
-        <v>7.93</v>
+        <v>16.18</v>
       </c>
       <c r="M4" t="n">
-        <v>1807433.12</v>
+        <v>26.98</v>
       </c>
       <c r="N4" t="n">
-        <v>8.99</v>
+        <v>4173085.48</v>
       </c>
       <c r="O4" t="n">
-        <v>3.7</v>
+        <v>14.22</v>
       </c>
       <c r="P4" t="n">
-        <v>1.42</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>45748</v>
+        <v>2.37</v>
       </c>
       <c r="R4" t="n">
-        <v>8950</v>
+        <v>139078</v>
       </c>
       <c r="S4" t="n">
-        <v>2978</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
-        <v>14</v>
+        <v>12270</v>
+      </c>
+      <c r="T4" t="n">
+        <v>18</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
       </c>
       <c r="V4" t="n">
-        <v>16.41029009859514</v>
+        <v>21</v>
+      </c>
+      <c r="W4" t="n">
+        <v>36.09538200677854</v>
+      </c>
+      <c r="X4" t="n">
+        <v>4.644549367100055</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>23.2535428740343</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -762,72 +804,81 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13.04</v>
+        <v>7569</v>
       </c>
       <c r="D5" t="n">
-        <v>8.380000000000001</v>
+        <v>3.06</v>
       </c>
       <c r="E5" t="n">
-        <v>1.32</v>
+        <v>11.55</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05</v>
+        <v>0.76</v>
       </c>
       <c r="G5" t="n">
-        <v>7906</v>
+        <v>5.22</v>
       </c>
       <c r="H5" t="n">
-        <v>19.07</v>
+        <v>1.17</v>
       </c>
       <c r="I5" t="n">
-        <v>23.25</v>
+        <v>925</v>
       </c>
       <c r="J5" t="n">
-        <v>20.11</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>49.7</v>
+        <v>7.56</v>
       </c>
       <c r="L5" t="n">
-        <v>5.73</v>
+        <v>5.92</v>
       </c>
       <c r="M5" t="n">
-        <v>2618348.58</v>
+        <v>13.7</v>
       </c>
       <c r="N5" t="n">
-        <v>9.81</v>
+        <v>146151.16</v>
       </c>
       <c r="O5" t="n">
-        <v>3.91</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>2.82</v>
+        <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>26645</v>
+        <v>2.18</v>
       </c>
       <c r="R5" t="n">
-        <v>6412</v>
+        <v>98692</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>31</v>
+        <v>3020</v>
+      </c>
+      <c r="T5" t="n">
+        <v>9</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
       </c>
       <c r="V5" t="n">
-        <v>19.10193873049559</v>
+        <v>20</v>
+      </c>
+      <c r="W5" t="n">
+        <v>34.24436618882645</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>19.82084189180693</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -836,66 +887,75 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15.76</v>
+        <v>-16843</v>
       </c>
       <c r="D6" t="n">
-        <v>12.14</v>
+        <v>19.56</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9</v>
+        <v>14.25</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07000000000000001</v>
+        <v>6.89</v>
       </c>
       <c r="G6" t="n">
-        <v>-7559</v>
+        <v>1.88</v>
       </c>
       <c r="H6" t="n">
-        <v>17.48</v>
+        <v>0.09</v>
       </c>
       <c r="I6" t="n">
-        <v>74.51000000000001</v>
+        <v>-17468</v>
       </c>
       <c r="J6" t="n">
-        <v>55.18</v>
+        <v>15.5</v>
       </c>
       <c r="K6" t="n">
-        <v>49.07</v>
+        <v>22.08</v>
       </c>
       <c r="L6" t="n">
-        <v>6.33</v>
+        <v>15.9</v>
       </c>
       <c r="M6" t="n">
-        <v>590971.02</v>
+        <v>7.93</v>
       </c>
       <c r="N6" t="n">
-        <v>16.89</v>
+        <v>1807433.12</v>
       </c>
       <c r="O6" t="n">
-        <v>4.15</v>
+        <v>8.99</v>
       </c>
       <c r="P6" t="n">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>118379</v>
+        <v>1.42</v>
       </c>
       <c r="R6" t="n">
-        <v>18869</v>
+        <v>45748</v>
       </c>
       <c r="S6" t="n">
-        <v>4102</v>
-      </c>
-      <c r="T6" t="inlineStr">
+        <v>8950</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2978</v>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="U6" t="n">
-        <v>21</v>
-      </c>
       <c r="V6" t="n">
-        <v>16.78883948962531</v>
+        <v>14</v>
+      </c>
+      <c r="W6" t="n">
+        <v>33.69686056943905</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>16.41029009859514</v>
       </c>
     </row>
   </sheetData>
